--- a/ky/downloads/data-excel/17.1.1.xlsx
+++ b/ky/downloads/data-excel/17.1.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="28830" windowHeight="5955"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>(в процентах  к ВВП)</t>
   </si>
@@ -304,7 +304,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -404,6 +404,24 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -688,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.140625" customWidth="1"/>
@@ -697,7 +715,7 @@
     <col min="16" max="20" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>25</v>
       </c>
@@ -720,7 +738,7 @@
       <c r="N1" s="26"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>19</v>
       </c>
@@ -743,7 +761,7 @@
       <c r="N2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
@@ -759,8 +777,9 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="U3" s="39"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>18</v>
       </c>
@@ -821,8 +840,11 @@
       <c r="T4" s="14">
         <v>2023</v>
       </c>
+      <c r="U4" s="40">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>20</v>
       </c>
@@ -883,8 +905,11 @@
       <c r="T5" s="38">
         <v>29.4</v>
       </c>
+      <c r="U5" s="41">
+        <v>29.4</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
@@ -945,8 +970,11 @@
       <c r="T6" s="30">
         <v>22.1</v>
       </c>
+      <c r="U6" s="42">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>21</v>
       </c>
@@ -1007,8 +1035,11 @@
       <c r="T7" s="30" t="s">
         <v>6</v>
       </c>
+      <c r="U7" s="42" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
         <v>26</v>
       </c>
@@ -1069,8 +1100,11 @@
       <c r="T8" s="30">
         <v>1.2</v>
       </c>
+      <c r="U8" s="42">
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
@@ -1131,8 +1165,11 @@
       <c r="T9" s="32">
         <v>6.1</v>
       </c>
+      <c r="U9" s="43">
+        <v>6.4</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>22</v>
       </c>
@@ -1193,8 +1230,11 @@
       <c r="T10" s="34">
         <v>0</v>
       </c>
+      <c r="U10" s="44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
       <c r="B11" s="8"/>
       <c r="C11" s="25"/>
@@ -1212,7 +1252,7 @@
       <c r="O11" s="26"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B12" s="8"/>
     </row>
   </sheetData>
